--- a/data/preliminaries/stellar/male/22-preliminary-r06-stellar-male.xlsx
+++ b/data/preliminaries/stellar/male/22-preliminary-r06-stellar-male.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>进入第4轮</t>
+          <t>未晋级</t>
         </is>
       </c>
     </row>
